--- a/media/Levels/Level.xlsx
+++ b/media/Levels/Level.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\oyush\OneDrive - 学校法人新潟総合学院 学校法人国際総合学園 学校法人大彦学園\デスクトップ\勉強\DoctorRemote\DoctorRemote_α\media\Levels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E7F4D4E-4E92-4C34-AE82-354D635EB6A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DA346A9D-2036-42C2-833F-69910CC8088F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{2739887D-75BF-488C-B937-CF17A666C93E}"/>
   </bookViews>
   <sheets>
-    <sheet name="levels" sheetId="1" r:id="rId1"/>
+    <sheet name="Level" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -26619,7 +26619,7 @@
         <v>0</v>
       </c>
       <c r="BY57">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="BZ57">
         <v>12</v>
@@ -27067,11 +27067,11 @@
       <c r="BW58">
         <v>12</v>
       </c>
-      <c r="BX58" s="6">
-        <v>2</v>
-      </c>
-      <c r="BY58">
-        <v>12</v>
+      <c r="BX58">
+        <v>12</v>
+      </c>
+      <c r="BY58" s="6">
+        <v>4</v>
       </c>
       <c r="BZ58">
         <v>12</v>
@@ -27519,14 +27519,14 @@
       <c r="BW59">
         <v>12</v>
       </c>
-      <c r="BX59" s="6">
-        <v>0</v>
+      <c r="BX59">
+        <v>12</v>
       </c>
       <c r="BY59">
         <v>12</v>
       </c>
-      <c r="BZ59">
-        <v>12</v>
+      <c r="BZ59" s="6">
+        <v>0</v>
       </c>
       <c r="CA59">
         <v>12</v>
@@ -27974,14 +27974,14 @@
       <c r="BX60">
         <v>12</v>
       </c>
-      <c r="BY60" s="6">
-        <v>0</v>
+      <c r="BY60">
+        <v>12</v>
       </c>
       <c r="BZ60">
         <v>12</v>
       </c>
-      <c r="CA60">
-        <v>12</v>
+      <c r="CA60" s="6">
+        <v>0</v>
       </c>
       <c r="CB60">
         <v>12</v>
@@ -28429,14 +28429,14 @@
       <c r="BY61">
         <v>12</v>
       </c>
-      <c r="BZ61" s="6">
+      <c r="BZ61">
+        <v>12</v>
+      </c>
+      <c r="CA61">
+        <v>12</v>
+      </c>
+      <c r="CB61" s="6">
         <v>4</v>
-      </c>
-      <c r="CA61">
-        <v>12</v>
-      </c>
-      <c r="CB61">
-        <v>12</v>
       </c>
       <c r="CC61">
         <v>12</v>
@@ -28884,14 +28884,14 @@
       <c r="BZ62">
         <v>12</v>
       </c>
-      <c r="CA62" s="6">
-        <v>0</v>
+      <c r="CA62">
+        <v>12</v>
       </c>
       <c r="CB62">
         <v>12</v>
       </c>
-      <c r="CC62">
-        <v>12</v>
+      <c r="CC62" s="6">
+        <v>0</v>
       </c>
       <c r="CD62">
         <v>12</v>
@@ -29339,14 +29339,14 @@
       <c r="CA63">
         <v>12</v>
       </c>
-      <c r="CB63" s="6">
-        <v>0</v>
+      <c r="CB63">
+        <v>12</v>
       </c>
       <c r="CC63">
         <v>12</v>
       </c>
-      <c r="CD63">
-        <v>12</v>
+      <c r="CD63" s="6">
+        <v>0</v>
       </c>
       <c r="CE63">
         <v>12</v>
@@ -29794,14 +29794,14 @@
       <c r="CB64">
         <v>12</v>
       </c>
-      <c r="CC64" s="6">
+      <c r="CC64">
+        <v>12</v>
+      </c>
+      <c r="CD64">
+        <v>12</v>
+      </c>
+      <c r="CE64" s="6">
         <v>4</v>
-      </c>
-      <c r="CD64">
-        <v>12</v>
-      </c>
-      <c r="CE64">
-        <v>12</v>
       </c>
       <c r="CF64">
         <v>12</v>
@@ -30216,29 +30216,20 @@
       <c r="BR65">
         <v>12</v>
       </c>
-      <c r="BS65">
-        <v>12</v>
-      </c>
-      <c r="BT65">
-        <v>12</v>
-      </c>
-      <c r="BU65">
-        <v>12</v>
-      </c>
-      <c r="BV65" s="1">
-        <v>11</v>
-      </c>
-      <c r="BW65" s="1">
-        <v>11</v>
-      </c>
-      <c r="BX65" s="1">
-        <v>11</v>
-      </c>
-      <c r="BY65" s="1">
-        <v>11</v>
-      </c>
-      <c r="BZ65" s="1">
-        <v>11</v>
+      <c r="BV65">
+        <v>12</v>
+      </c>
+      <c r="BW65">
+        <v>12</v>
+      </c>
+      <c r="BX65">
+        <v>12</v>
+      </c>
+      <c r="BY65">
+        <v>12</v>
+      </c>
+      <c r="BZ65">
+        <v>12</v>
       </c>
       <c r="CA65">
         <v>12</v>
@@ -30249,14 +30240,14 @@
       <c r="CC65">
         <v>12</v>
       </c>
-      <c r="CD65" s="6">
-        <v>0</v>
+      <c r="CD65">
+        <v>12</v>
       </c>
       <c r="CE65">
         <v>12</v>
       </c>
-      <c r="CF65">
-        <v>12</v>
+      <c r="CF65" s="6">
+        <v>0</v>
       </c>
       <c r="CG65">
         <v>12</v>
@@ -30668,37 +30659,37 @@
       <c r="BR66" s="2">
         <v>0</v>
       </c>
-      <c r="BS66" s="2">
-        <v>0</v>
-      </c>
-      <c r="BT66" s="2">
-        <v>0</v>
-      </c>
-      <c r="BU66" s="2">
-        <v>0</v>
-      </c>
-      <c r="BV66" s="2">
-        <v>0</v>
-      </c>
-      <c r="BW66" s="2">
-        <v>0</v>
-      </c>
-      <c r="BX66" s="2">
-        <v>0</v>
-      </c>
-      <c r="BY66" s="2">
-        <v>0</v>
-      </c>
-      <c r="BZ66" s="2">
-        <v>0</v>
-      </c>
-      <c r="CA66" s="2">
-        <v>0</v>
-      </c>
-      <c r="CB66" s="2">
-        <v>0</v>
-      </c>
-      <c r="CC66" s="2">
+      <c r="BS66" s="1">
+        <v>0</v>
+      </c>
+      <c r="BT66" s="1">
+        <v>0</v>
+      </c>
+      <c r="BU66" s="1">
+        <v>0</v>
+      </c>
+      <c r="BV66" s="1">
+        <v>0</v>
+      </c>
+      <c r="BW66" s="1">
+        <v>0</v>
+      </c>
+      <c r="BX66" s="1">
+        <v>11</v>
+      </c>
+      <c r="BY66" s="1">
+        <v>0</v>
+      </c>
+      <c r="BZ66" s="1">
+        <v>0</v>
+      </c>
+      <c r="CA66" s="1">
+        <v>0</v>
+      </c>
+      <c r="CB66" s="1">
+        <v>0</v>
+      </c>
+      <c r="CC66" s="1">
         <v>0</v>
       </c>
       <c r="CD66" s="2">
@@ -39253,37 +39244,37 @@
       <c r="BR85" s="2">
         <v>0</v>
       </c>
-      <c r="BS85" s="2">
-        <v>0</v>
-      </c>
-      <c r="BT85" s="2">
-        <v>0</v>
-      </c>
-      <c r="BU85" s="2">
-        <v>0</v>
-      </c>
-      <c r="BV85" s="2">
-        <v>0</v>
-      </c>
-      <c r="BW85" s="2">
-        <v>0</v>
-      </c>
-      <c r="BX85" s="2">
-        <v>0</v>
-      </c>
-      <c r="BY85" s="2">
-        <v>0</v>
-      </c>
-      <c r="BZ85" s="2">
-        <v>0</v>
-      </c>
-      <c r="CA85" s="2">
-        <v>0</v>
-      </c>
-      <c r="CB85" s="2">
-        <v>0</v>
-      </c>
-      <c r="CC85" s="2">
+      <c r="BS85" s="1">
+        <v>0</v>
+      </c>
+      <c r="BT85" s="1">
+        <v>0</v>
+      </c>
+      <c r="BU85" s="1">
+        <v>0</v>
+      </c>
+      <c r="BV85" s="1">
+        <v>0</v>
+      </c>
+      <c r="BW85" s="1">
+        <v>0</v>
+      </c>
+      <c r="BX85" s="1">
+        <v>11</v>
+      </c>
+      <c r="BY85" s="1">
+        <v>0</v>
+      </c>
+      <c r="BZ85" s="1">
+        <v>0</v>
+      </c>
+      <c r="CA85" s="1">
+        <v>0</v>
+      </c>
+      <c r="CB85" s="1">
+        <v>0</v>
+      </c>
+      <c r="CC85" s="1">
         <v>0</v>
       </c>
       <c r="CD85" s="2">
@@ -39702,8 +39693,8 @@
       <c r="BQ86">
         <v>12</v>
       </c>
-      <c r="BR86" s="6">
-        <v>0</v>
+      <c r="BR86">
+        <v>12</v>
       </c>
       <c r="BS86">
         <v>12</v>
@@ -39714,20 +39705,20 @@
       <c r="BU86">
         <v>12</v>
       </c>
-      <c r="BV86" s="1">
-        <v>11</v>
-      </c>
-      <c r="BW86" s="1">
-        <v>11</v>
-      </c>
-      <c r="BX86" s="1">
-        <v>11</v>
-      </c>
-      <c r="BY86" s="1">
-        <v>11</v>
-      </c>
-      <c r="BZ86" s="1">
-        <v>11</v>
+      <c r="BV86">
+        <v>12</v>
+      </c>
+      <c r="BW86">
+        <v>12</v>
+      </c>
+      <c r="BX86">
+        <v>12</v>
+      </c>
+      <c r="BY86">
+        <v>12</v>
+      </c>
+      <c r="BZ86">
+        <v>12</v>
       </c>
       <c r="CA86">
         <v>12</v>
@@ -40157,8 +40148,8 @@
       <c r="BR87">
         <v>12</v>
       </c>
-      <c r="BS87" s="6">
-        <v>3</v>
+      <c r="BS87">
+        <v>12</v>
       </c>
       <c r="BT87">
         <v>12</v>
@@ -40612,8 +40603,8 @@
       <c r="BS88">
         <v>12</v>
       </c>
-      <c r="BT88" s="6">
-        <v>0</v>
+      <c r="BT88">
+        <v>12</v>
       </c>
       <c r="BU88">
         <v>12</v>
@@ -41067,8 +41058,8 @@
       <c r="BT89">
         <v>12</v>
       </c>
-      <c r="BU89" s="6">
-        <v>0</v>
+      <c r="BU89">
+        <v>12</v>
       </c>
       <c r="BV89">
         <v>12</v>
@@ -41522,8 +41513,8 @@
       <c r="BU90">
         <v>12</v>
       </c>
-      <c r="BV90" s="6">
-        <v>3</v>
+      <c r="BV90">
+        <v>12</v>
       </c>
       <c r="BW90">
         <v>12</v>
@@ -41977,8 +41968,8 @@
       <c r="BV91">
         <v>12</v>
       </c>
-      <c r="BW91" s="6">
-        <v>0</v>
+      <c r="BW91">
+        <v>12</v>
       </c>
       <c r="BX91">
         <v>12</v>
@@ -42432,8 +42423,8 @@
       <c r="BW92">
         <v>12</v>
       </c>
-      <c r="BX92" s="6">
-        <v>0</v>
+      <c r="BX92">
+        <v>12</v>
       </c>
       <c r="BY92">
         <v>12</v>
@@ -42884,8 +42875,8 @@
       <c r="BW93">
         <v>12</v>
       </c>
-      <c r="BX93" s="6">
-        <v>2</v>
+      <c r="BX93">
+        <v>12</v>
       </c>
       <c r="BY93">
         <v>12</v>
@@ -43336,8 +43327,8 @@
       <c r="BW94">
         <v>12</v>
       </c>
-      <c r="BX94" s="6">
-        <v>0</v>
+      <c r="BX94">
+        <v>12</v>
       </c>
       <c r="BY94">
         <v>12</v>
@@ -43788,8 +43779,8 @@
       <c r="BW95">
         <v>12</v>
       </c>
-      <c r="BX95" s="6">
-        <v>0</v>
+      <c r="BX95">
+        <v>12</v>
       </c>
       <c r="BY95">
         <v>12</v>
@@ -44240,8 +44231,8 @@
       <c r="BW96">
         <v>12</v>
       </c>
-      <c r="BX96" s="6">
-        <v>2</v>
+      <c r="BX96">
+        <v>12</v>
       </c>
       <c r="BY96">
         <v>12</v>
@@ -44692,8 +44683,8 @@
       <c r="BW97">
         <v>12</v>
       </c>
-      <c r="BX97" s="6">
-        <v>0</v>
+      <c r="BX97">
+        <v>12</v>
       </c>
       <c r="BY97">
         <v>12</v>
@@ -45144,8 +45135,8 @@
       <c r="BW98">
         <v>12</v>
       </c>
-      <c r="BX98" s="6">
-        <v>0</v>
+      <c r="BX98">
+        <v>12</v>
       </c>
       <c r="BY98">
         <v>12</v>
@@ -45596,8 +45587,8 @@
       <c r="BW99">
         <v>12</v>
       </c>
-      <c r="BX99" s="6">
-        <v>2</v>
+      <c r="BX99">
+        <v>12</v>
       </c>
       <c r="BY99">
         <v>12</v>
@@ -46048,8 +46039,8 @@
       <c r="BW100">
         <v>12</v>
       </c>
-      <c r="BX100" s="6">
-        <v>0</v>
+      <c r="BX100">
+        <v>12</v>
       </c>
       <c r="BY100">
         <v>12</v>
@@ -46500,8 +46491,8 @@
       <c r="BW101">
         <v>12</v>
       </c>
-      <c r="BX101" s="6">
-        <v>0</v>
+      <c r="BX101">
+        <v>12</v>
       </c>
       <c r="BY101">
         <v>12</v>
@@ -46952,8 +46943,8 @@
       <c r="BW102">
         <v>12</v>
       </c>
-      <c r="BX102" s="6">
-        <v>2</v>
+      <c r="BX102">
+        <v>12</v>
       </c>
       <c r="BY102">
         <v>12</v>
@@ -47404,8 +47395,8 @@
       <c r="BW103">
         <v>12</v>
       </c>
-      <c r="BX103" s="6">
-        <v>0</v>
+      <c r="BX103">
+        <v>12</v>
       </c>
       <c r="BY103">
         <v>12</v>

--- a/media/Levels/Level.xlsx
+++ b/media/Levels/Level.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\oyush\OneDrive - 学校法人新潟総合学院 学校法人国際総合学園 学校法人大彦学園\デスクトップ\勉強\DoctorRemote\DoctorRemote_α\media\Levels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DA346A9D-2036-42C2-833F-69910CC8088F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{322EF090-0E48-4350-808E-6892A9300BD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{2739887D-75BF-488C-B937-CF17A666C93E}"/>
   </bookViews>
@@ -26619,7 +26619,7 @@
         <v>0</v>
       </c>
       <c r="BY57">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="BZ57">
         <v>12</v>
@@ -30214,6 +30214,15 @@
         <v>12</v>
       </c>
       <c r="BR65">
+        <v>12</v>
+      </c>
+      <c r="BS65">
+        <v>12</v>
+      </c>
+      <c r="BT65">
+        <v>12</v>
+      </c>
+      <c r="BU65">
         <v>12</v>
       </c>
       <c r="BV65">

--- a/media/Levels/Level.xlsx
+++ b/media/Levels/Level.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\oyush\OneDrive - 学校法人新潟総合学院 学校法人国際総合学園 学校法人大彦学園\デスクトップ\勉強\DoctorRemote\DoctorRemote_α\media\Levels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{322EF090-0E48-4350-808E-6892A9300BD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA7116CB-CCD6-46F1-BE78-9110ABF76D3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{2739887D-75BF-488C-B937-CF17A666C93E}"/>
   </bookViews>
@@ -1100,7 +1100,7 @@
         <v>0</v>
       </c>
       <c r="H1" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I1" s="6">
         <v>0</v>
@@ -1109,7 +1109,7 @@
         <v>0</v>
       </c>
       <c r="K1" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L1" s="6">
         <v>0</v>
@@ -1118,7 +1118,7 @@
         <v>0</v>
       </c>
       <c r="N1" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O1" s="6">
         <v>0</v>
@@ -1127,7 +1127,7 @@
         <v>0</v>
       </c>
       <c r="Q1" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R1" s="6">
         <v>0</v>
@@ -1136,7 +1136,7 @@
         <v>0</v>
       </c>
       <c r="T1" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U1" s="6">
         <v>0</v>
@@ -1145,7 +1145,7 @@
         <v>0</v>
       </c>
       <c r="W1" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X1" s="6">
         <v>0</v>
@@ -1154,7 +1154,7 @@
         <v>0</v>
       </c>
       <c r="Z1" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA1" s="6">
         <v>0</v>
@@ -1163,7 +1163,7 @@
         <v>0</v>
       </c>
       <c r="AC1" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD1" s="6">
         <v>0</v>
@@ -1172,7 +1172,7 @@
         <v>0</v>
       </c>
       <c r="AF1" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG1" s="6">
         <v>0</v>
@@ -1181,7 +1181,7 @@
         <v>0</v>
       </c>
       <c r="AI1" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ1" s="6">
         <v>0</v>
@@ -1190,7 +1190,7 @@
         <v>0</v>
       </c>
       <c r="AL1" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM1" s="6">
         <v>0</v>
@@ -1199,7 +1199,7 @@
         <v>0</v>
       </c>
       <c r="AO1" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP1" s="6">
         <v>0</v>
@@ -1208,7 +1208,7 @@
         <v>0</v>
       </c>
       <c r="AR1" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS1" s="6">
         <v>0</v>
@@ -1217,7 +1217,7 @@
         <v>0</v>
       </c>
       <c r="AU1" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV1" s="6">
         <v>0</v>
@@ -1226,7 +1226,7 @@
         <v>0</v>
       </c>
       <c r="AX1" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY1" s="6">
         <v>0</v>
@@ -1235,7 +1235,7 @@
         <v>0</v>
       </c>
       <c r="BA1" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB1" s="6">
         <v>0</v>
@@ -1244,7 +1244,7 @@
         <v>0</v>
       </c>
       <c r="BD1" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BE1" s="6">
         <v>0</v>
@@ -1253,7 +1253,7 @@
         <v>0</v>
       </c>
       <c r="BG1" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BH1" s="6">
         <v>0</v>
@@ -1262,7 +1262,7 @@
         <v>0</v>
       </c>
       <c r="BJ1" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BK1" s="6">
         <v>0</v>
@@ -1271,7 +1271,7 @@
         <v>0</v>
       </c>
       <c r="BM1" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BN1" s="6">
         <v>0</v>
@@ -1280,7 +1280,7 @@
         <v>0</v>
       </c>
       <c r="BP1" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BQ1" s="6">
         <v>0</v>
@@ -1289,7 +1289,7 @@
         <v>0</v>
       </c>
       <c r="BS1" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BT1" s="6">
         <v>0</v>
@@ -1298,16 +1298,16 @@
         <v>0</v>
       </c>
       <c r="BV1" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BW1" s="6">
         <v>0</v>
       </c>
       <c r="BX1" s="6">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="BY1" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BZ1" s="6">
         <v>0</v>
@@ -1316,7 +1316,7 @@
         <v>0</v>
       </c>
       <c r="CB1" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CC1" s="6">
         <v>0</v>
@@ -1325,7 +1325,7 @@
         <v>0</v>
       </c>
       <c r="CE1" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CF1" s="6">
         <v>0</v>
@@ -1334,7 +1334,7 @@
         <v>0</v>
       </c>
       <c r="CH1" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CI1" s="6">
         <v>0</v>
@@ -1343,7 +1343,7 @@
         <v>0</v>
       </c>
       <c r="CK1" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CL1" s="6">
         <v>0</v>
@@ -1352,7 +1352,7 @@
         <v>0</v>
       </c>
       <c r="CN1" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CO1" s="6">
         <v>0</v>
@@ -1361,7 +1361,7 @@
         <v>0</v>
       </c>
       <c r="CQ1" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CR1" s="6">
         <v>0</v>
@@ -1370,7 +1370,7 @@
         <v>0</v>
       </c>
       <c r="CT1" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CU1" s="6">
         <v>0</v>
@@ -1379,7 +1379,7 @@
         <v>0</v>
       </c>
       <c r="CW1" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CX1" s="6">
         <v>0</v>
@@ -1388,7 +1388,7 @@
         <v>0</v>
       </c>
       <c r="CZ1" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DA1" s="6">
         <v>0</v>
@@ -1397,7 +1397,7 @@
         <v>0</v>
       </c>
       <c r="DC1" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DD1" s="6">
         <v>0</v>
@@ -1406,7 +1406,7 @@
         <v>0</v>
       </c>
       <c r="DF1" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DG1" s="6">
         <v>0</v>
@@ -1415,7 +1415,7 @@
         <v>0</v>
       </c>
       <c r="DI1" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DJ1" s="6">
         <v>0</v>
@@ -1424,7 +1424,7 @@
         <v>0</v>
       </c>
       <c r="DL1" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DM1" s="6">
         <v>0</v>
@@ -1433,7 +1433,7 @@
         <v>0</v>
       </c>
       <c r="DO1" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DP1" s="6">
         <v>0</v>
@@ -1442,7 +1442,7 @@
         <v>0</v>
       </c>
       <c r="DR1" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS1" s="6">
         <v>0</v>
@@ -1451,7 +1451,7 @@
         <v>0</v>
       </c>
       <c r="DU1" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DV1" s="6">
         <v>0</v>
@@ -1460,7 +1460,7 @@
         <v>0</v>
       </c>
       <c r="DX1" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DY1" s="6">
         <v>0</v>
@@ -1469,7 +1469,7 @@
         <v>0</v>
       </c>
       <c r="EA1" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EB1" s="6">
         <v>0</v>
@@ -1478,7 +1478,7 @@
         <v>0</v>
       </c>
       <c r="ED1" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EE1" s="6">
         <v>0</v>
@@ -1487,7 +1487,7 @@
         <v>0</v>
       </c>
       <c r="EG1" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EH1" s="6">
         <v>0</v>
@@ -1496,7 +1496,7 @@
         <v>0</v>
       </c>
       <c r="EJ1" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EK1" s="6">
         <v>0</v>
@@ -1505,7 +1505,7 @@
         <v>0</v>
       </c>
       <c r="EM1" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EN1" s="6">
         <v>0</v>
@@ -4243,7 +4243,7 @@
     </row>
     <row r="8" spans="1:150" x14ac:dyDescent="0.45">
       <c r="A8" s="6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B8">
         <v>12</v>
@@ -4690,7 +4690,7 @@
         <v>12</v>
       </c>
       <c r="ET8" s="6">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:150" x14ac:dyDescent="0.45">
@@ -5599,7 +5599,7 @@
     </row>
     <row r="11" spans="1:150" x14ac:dyDescent="0.45">
       <c r="A11" s="6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B11">
         <v>12</v>
@@ -6046,7 +6046,7 @@
         <v>12</v>
       </c>
       <c r="ET11" s="6">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:150" x14ac:dyDescent="0.45">
@@ -6955,7 +6955,7 @@
     </row>
     <row r="14" spans="1:150" x14ac:dyDescent="0.45">
       <c r="A14" s="6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B14">
         <v>12</v>
@@ -7402,7 +7402,7 @@
         <v>12</v>
       </c>
       <c r="ET14" s="6">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:150" x14ac:dyDescent="0.45">
@@ -8311,7 +8311,7 @@
     </row>
     <row r="17" spans="1:150" x14ac:dyDescent="0.45">
       <c r="A17" s="6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B17">
         <v>12</v>
@@ -8758,7 +8758,7 @@
         <v>12</v>
       </c>
       <c r="ET17" s="6">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:150" x14ac:dyDescent="0.45">
@@ -9667,7 +9667,7 @@
     </row>
     <row r="20" spans="1:150" x14ac:dyDescent="0.45">
       <c r="A20" s="6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B20">
         <v>12</v>
@@ -10114,7 +10114,7 @@
         <v>12</v>
       </c>
       <c r="ET20" s="6">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:150" x14ac:dyDescent="0.45">
@@ -11023,7 +11023,7 @@
     </row>
     <row r="23" spans="1:150" x14ac:dyDescent="0.45">
       <c r="A23" s="6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B23">
         <v>12</v>
@@ -11470,7 +11470,7 @@
         <v>12</v>
       </c>
       <c r="ET23" s="6">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:150" x14ac:dyDescent="0.45">
@@ -12379,7 +12379,7 @@
     </row>
     <row r="26" spans="1:150" x14ac:dyDescent="0.45">
       <c r="A26" s="6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B26">
         <v>12</v>
@@ -12826,7 +12826,7 @@
         <v>12</v>
       </c>
       <c r="ET26" s="6">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:150" x14ac:dyDescent="0.45">
@@ -13735,7 +13735,7 @@
     </row>
     <row r="29" spans="1:150" x14ac:dyDescent="0.45">
       <c r="A29" s="6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B29">
         <v>12</v>
@@ -14182,7 +14182,7 @@
         <v>12</v>
       </c>
       <c r="ET29" s="6">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:150" x14ac:dyDescent="0.45">
@@ -15091,7 +15091,7 @@
     </row>
     <row r="32" spans="1:150" x14ac:dyDescent="0.45">
       <c r="A32" s="6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B32">
         <v>12</v>
@@ -15538,7 +15538,7 @@
         <v>12</v>
       </c>
       <c r="ET32" s="6">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:150" x14ac:dyDescent="0.45">
@@ -16447,7 +16447,7 @@
     </row>
     <row r="35" spans="1:150" x14ac:dyDescent="0.45">
       <c r="A35" s="6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B35">
         <v>12</v>
@@ -16894,7 +16894,7 @@
         <v>12</v>
       </c>
       <c r="ET35" s="6">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:150" x14ac:dyDescent="0.45">
@@ -17803,7 +17803,7 @@
     </row>
     <row r="38" spans="1:150" x14ac:dyDescent="0.45">
       <c r="A38" s="6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B38">
         <v>12</v>
@@ -18250,7 +18250,7 @@
         <v>12</v>
       </c>
       <c r="ET38" s="6">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:150" x14ac:dyDescent="0.45">
@@ -19159,7 +19159,7 @@
     </row>
     <row r="41" spans="1:150" x14ac:dyDescent="0.45">
       <c r="A41" s="6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B41">
         <v>12</v>
@@ -19606,7 +19606,7 @@
         <v>12</v>
       </c>
       <c r="ET41" s="6">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:150" x14ac:dyDescent="0.45">
@@ -20515,7 +20515,7 @@
     </row>
     <row r="44" spans="1:150" x14ac:dyDescent="0.45">
       <c r="A44" s="6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B44">
         <v>12</v>
@@ -20962,7 +20962,7 @@
         <v>12</v>
       </c>
       <c r="ET44" s="6">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45" spans="1:150" x14ac:dyDescent="0.45">
@@ -21871,7 +21871,7 @@
     </row>
     <row r="47" spans="1:150" x14ac:dyDescent="0.45">
       <c r="A47" s="6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B47">
         <v>12</v>
@@ -22318,7 +22318,7 @@
         <v>12</v>
       </c>
       <c r="ET47" s="6">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48" spans="1:150" x14ac:dyDescent="0.45">
@@ -23227,7 +23227,7 @@
     </row>
     <row r="50" spans="1:150" x14ac:dyDescent="0.45">
       <c r="A50" s="6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B50">
         <v>12</v>
@@ -23674,7 +23674,7 @@
         <v>12</v>
       </c>
       <c r="ET50" s="6">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51" spans="1:150" x14ac:dyDescent="0.45">
@@ -24583,7 +24583,7 @@
     </row>
     <row r="53" spans="1:150" x14ac:dyDescent="0.45">
       <c r="A53" s="6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B53">
         <v>12</v>
@@ -25030,7 +25030,7 @@
         <v>12</v>
       </c>
       <c r="ET53" s="6">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54" spans="1:150" x14ac:dyDescent="0.45">
@@ -25939,7 +25939,7 @@
     </row>
     <row r="56" spans="1:150" x14ac:dyDescent="0.45">
       <c r="A56" s="6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B56">
         <v>12</v>
@@ -26386,7 +26386,7 @@
         <v>12</v>
       </c>
       <c r="ET56" s="6">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57" spans="1:150" x14ac:dyDescent="0.45">
@@ -27295,7 +27295,7 @@
     </row>
     <row r="59" spans="1:150" x14ac:dyDescent="0.45">
       <c r="A59" s="6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B59">
         <v>12</v>
@@ -27742,7 +27742,7 @@
         <v>12</v>
       </c>
       <c r="ET59" s="6">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60" spans="1:150" x14ac:dyDescent="0.45">
@@ -28651,7 +28651,7 @@
     </row>
     <row r="62" spans="1:150" x14ac:dyDescent="0.45">
       <c r="A62" s="6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B62">
         <v>12</v>
@@ -29098,7 +29098,7 @@
         <v>12</v>
       </c>
       <c r="ET62" s="6">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63" spans="1:150" x14ac:dyDescent="0.45">
@@ -30007,7 +30007,7 @@
     </row>
     <row r="65" spans="1:150" x14ac:dyDescent="0.45">
       <c r="A65" s="6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B65">
         <v>12</v>
@@ -30454,7 +30454,7 @@
         <v>12</v>
       </c>
       <c r="ET65" s="6">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66" spans="1:150" x14ac:dyDescent="0.45">
@@ -31363,7 +31363,7 @@
     </row>
     <row r="68" spans="1:150" x14ac:dyDescent="0.45">
       <c r="A68" s="6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B68">
         <v>12</v>
@@ -31810,7 +31810,7 @@
         <v>12</v>
       </c>
       <c r="ET68" s="6">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69" spans="1:150" x14ac:dyDescent="0.45">
@@ -32719,7 +32719,7 @@
     </row>
     <row r="71" spans="1:150" x14ac:dyDescent="0.45">
       <c r="A71" s="6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B71">
         <v>12</v>
@@ -33166,7 +33166,7 @@
         <v>12</v>
       </c>
       <c r="ET71" s="6">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72" spans="1:150" x14ac:dyDescent="0.45">
@@ -34075,7 +34075,7 @@
     </row>
     <row r="74" spans="1:150" x14ac:dyDescent="0.45">
       <c r="A74" s="6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B74">
         <v>12</v>
@@ -34522,12 +34522,12 @@
         <v>12</v>
       </c>
       <c r="ET74" s="6">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75" spans="1:150" x14ac:dyDescent="0.45">
       <c r="A75" s="6">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="B75" s="6">
         <v>0</v>
@@ -34974,7 +34974,7 @@
         <v>0</v>
       </c>
       <c r="ET75" s="6">
-        <v>0</v>
+        <v>14</v>
       </c>
     </row>
     <row r="76" spans="1:150" x14ac:dyDescent="0.45">
@@ -35428,7 +35428,7 @@
     </row>
     <row r="77" spans="1:150" x14ac:dyDescent="0.45">
       <c r="A77" s="6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B77">
         <v>12</v>
@@ -35875,7 +35875,7 @@
         <v>12</v>
       </c>
       <c r="ET77" s="6">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78" spans="1:150" x14ac:dyDescent="0.45">
@@ -36784,7 +36784,7 @@
     </row>
     <row r="80" spans="1:150" x14ac:dyDescent="0.45">
       <c r="A80" s="6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B80">
         <v>12</v>
@@ -37231,7 +37231,7 @@
         <v>12</v>
       </c>
       <c r="ET80" s="6">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81" spans="1:150" x14ac:dyDescent="0.45">
@@ -38140,7 +38140,7 @@
     </row>
     <row r="83" spans="1:150" x14ac:dyDescent="0.45">
       <c r="A83" s="6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B83">
         <v>12</v>
@@ -38587,7 +38587,7 @@
         <v>12</v>
       </c>
       <c r="ET83" s="6">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84" spans="1:150" x14ac:dyDescent="0.45">
@@ -39496,7 +39496,7 @@
     </row>
     <row r="86" spans="1:150" x14ac:dyDescent="0.45">
       <c r="A86" s="6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B86">
         <v>12</v>
@@ -39943,7 +39943,7 @@
         <v>12</v>
       </c>
       <c r="ET86" s="6">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87" spans="1:150" x14ac:dyDescent="0.45">
@@ -40852,7 +40852,7 @@
     </row>
     <row r="89" spans="1:150" x14ac:dyDescent="0.45">
       <c r="A89" s="6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B89">
         <v>12</v>
@@ -41299,7 +41299,7 @@
         <v>12</v>
       </c>
       <c r="ET89" s="6">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90" spans="1:150" x14ac:dyDescent="0.45">
@@ -42208,7 +42208,7 @@
     </row>
     <row r="92" spans="1:150" x14ac:dyDescent="0.45">
       <c r="A92" s="6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B92">
         <v>12</v>
@@ -42655,7 +42655,7 @@
         <v>12</v>
       </c>
       <c r="ET92" s="6">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93" spans="1:150" x14ac:dyDescent="0.45">
@@ -43564,7 +43564,7 @@
     </row>
     <row r="95" spans="1:150" x14ac:dyDescent="0.45">
       <c r="A95" s="6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B95">
         <v>12</v>
@@ -44011,7 +44011,7 @@
         <v>12</v>
       </c>
       <c r="ET95" s="6">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96" spans="1:150" x14ac:dyDescent="0.45">
@@ -44920,7 +44920,7 @@
     </row>
     <row r="98" spans="1:150" x14ac:dyDescent="0.45">
       <c r="A98" s="6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B98">
         <v>12</v>
@@ -45367,7 +45367,7 @@
         <v>12</v>
       </c>
       <c r="ET98" s="6">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99" spans="1:150" x14ac:dyDescent="0.45">
@@ -46276,7 +46276,7 @@
     </row>
     <row r="101" spans="1:150" x14ac:dyDescent="0.45">
       <c r="A101" s="6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B101">
         <v>12</v>
@@ -46723,7 +46723,7 @@
         <v>12</v>
       </c>
       <c r="ET101" s="6">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="102" spans="1:150" x14ac:dyDescent="0.45">
@@ -47632,7 +47632,7 @@
     </row>
     <row r="104" spans="1:150" x14ac:dyDescent="0.45">
       <c r="A104" s="6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B104">
         <v>12</v>
@@ -48079,7 +48079,7 @@
         <v>12</v>
       </c>
       <c r="ET104" s="6">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105" spans="1:150" x14ac:dyDescent="0.45">
@@ -48988,7 +48988,7 @@
     </row>
     <row r="107" spans="1:150" x14ac:dyDescent="0.45">
       <c r="A107" s="6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B107">
         <v>12</v>
@@ -49435,7 +49435,7 @@
         <v>12</v>
       </c>
       <c r="ET107" s="6">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108" spans="1:150" x14ac:dyDescent="0.45">
@@ -50344,7 +50344,7 @@
     </row>
     <row r="110" spans="1:150" x14ac:dyDescent="0.45">
       <c r="A110" s="6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B110">
         <v>12</v>
@@ -50791,7 +50791,7 @@
         <v>12</v>
       </c>
       <c r="ET110" s="6">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="111" spans="1:150" x14ac:dyDescent="0.45">
@@ -51700,7 +51700,7 @@
     </row>
     <row r="113" spans="1:150" x14ac:dyDescent="0.45">
       <c r="A113" s="6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B113">
         <v>12</v>
@@ -52147,7 +52147,7 @@
         <v>12</v>
       </c>
       <c r="ET113" s="6">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="114" spans="1:150" x14ac:dyDescent="0.45">
@@ -53056,7 +53056,7 @@
     </row>
     <row r="116" spans="1:150" x14ac:dyDescent="0.45">
       <c r="A116" s="6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B116">
         <v>12</v>
@@ -53503,7 +53503,7 @@
         <v>12</v>
       </c>
       <c r="ET116" s="6">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="117" spans="1:150" x14ac:dyDescent="0.45">
@@ -54412,7 +54412,7 @@
     </row>
     <row r="119" spans="1:150" x14ac:dyDescent="0.45">
       <c r="A119" s="6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B119">
         <v>12</v>
@@ -54844,7 +54844,7 @@
         <v>12</v>
       </c>
       <c r="ET119" s="6">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="120" spans="1:150" x14ac:dyDescent="0.45">
@@ -55753,7 +55753,7 @@
     </row>
     <row r="122" spans="1:150" x14ac:dyDescent="0.45">
       <c r="A122" s="6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B122">
         <v>12</v>
@@ -56200,7 +56200,7 @@
         <v>12</v>
       </c>
       <c r="ET122" s="6">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="123" spans="1:150" x14ac:dyDescent="0.45">
@@ -57109,7 +57109,7 @@
     </row>
     <row r="125" spans="1:150" x14ac:dyDescent="0.45">
       <c r="A125" s="6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B125">
         <v>12</v>
@@ -57556,7 +57556,7 @@
         <v>12</v>
       </c>
       <c r="ET125" s="6">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="126" spans="1:150" x14ac:dyDescent="0.45">
@@ -58465,7 +58465,7 @@
     </row>
     <row r="128" spans="1:150" x14ac:dyDescent="0.45">
       <c r="A128" s="6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B128">
         <v>12</v>
@@ -58912,7 +58912,7 @@
         <v>12</v>
       </c>
       <c r="ET128" s="6">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="129" spans="1:150" x14ac:dyDescent="0.45">
@@ -59821,7 +59821,7 @@
     </row>
     <row r="131" spans="1:150" x14ac:dyDescent="0.45">
       <c r="A131" s="6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B131">
         <v>12</v>
@@ -60268,7 +60268,7 @@
         <v>12</v>
       </c>
       <c r="ET131" s="6">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="132" spans="1:150" x14ac:dyDescent="0.45">
@@ -61177,7 +61177,7 @@
     </row>
     <row r="134" spans="1:150" x14ac:dyDescent="0.45">
       <c r="A134" s="6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B134">
         <v>12</v>
@@ -61624,7 +61624,7 @@
         <v>12</v>
       </c>
       <c r="ET134" s="6">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="135" spans="1:150" x14ac:dyDescent="0.45">
@@ -62533,7 +62533,7 @@
     </row>
     <row r="137" spans="1:150" x14ac:dyDescent="0.45">
       <c r="A137" s="6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B137">
         <v>12</v>
@@ -62980,7 +62980,7 @@
         <v>12</v>
       </c>
       <c r="ET137" s="6">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="138" spans="1:150" x14ac:dyDescent="0.45">
@@ -63889,7 +63889,7 @@
     </row>
     <row r="140" spans="1:150" x14ac:dyDescent="0.45">
       <c r="A140" s="6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B140">
         <v>12</v>
@@ -64336,7 +64336,7 @@
         <v>12</v>
       </c>
       <c r="ET140" s="6">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="141" spans="1:150" x14ac:dyDescent="0.45">
@@ -65245,7 +65245,7 @@
     </row>
     <row r="143" spans="1:150" x14ac:dyDescent="0.45">
       <c r="A143" s="6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B143">
         <v>12</v>
@@ -65692,7 +65692,7 @@
         <v>12</v>
       </c>
       <c r="ET143" s="6">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="144" spans="1:150" x14ac:dyDescent="0.45">
@@ -68421,7 +68421,7 @@
         <v>0</v>
       </c>
       <c r="H150" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I150" s="6">
         <v>0</v>
@@ -68430,7 +68430,7 @@
         <v>0</v>
       </c>
       <c r="K150" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L150" s="6">
         <v>0</v>
@@ -68439,7 +68439,7 @@
         <v>0</v>
       </c>
       <c r="N150" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O150" s="6">
         <v>0</v>
@@ -68448,7 +68448,7 @@
         <v>0</v>
       </c>
       <c r="Q150" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R150" s="6">
         <v>0</v>
@@ -68457,7 +68457,7 @@
         <v>0</v>
       </c>
       <c r="T150" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U150" s="6">
         <v>0</v>
@@ -68466,7 +68466,7 @@
         <v>0</v>
       </c>
       <c r="W150" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X150" s="6">
         <v>0</v>
@@ -68475,7 +68475,7 @@
         <v>0</v>
       </c>
       <c r="Z150" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA150" s="6">
         <v>0</v>
@@ -68484,7 +68484,7 @@
         <v>0</v>
       </c>
       <c r="AC150" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD150" s="6">
         <v>0</v>
@@ -68493,7 +68493,7 @@
         <v>0</v>
       </c>
       <c r="AF150" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG150" s="6">
         <v>0</v>
@@ -68502,7 +68502,7 @@
         <v>0</v>
       </c>
       <c r="AI150" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ150" s="6">
         <v>0</v>
@@ -68511,7 +68511,7 @@
         <v>0</v>
       </c>
       <c r="AL150" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM150" s="6">
         <v>0</v>
@@ -68520,7 +68520,7 @@
         <v>0</v>
       </c>
       <c r="AO150" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP150" s="6">
         <v>0</v>
@@ -68529,7 +68529,7 @@
         <v>0</v>
       </c>
       <c r="AR150" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS150" s="6">
         <v>0</v>
@@ -68538,7 +68538,7 @@
         <v>0</v>
       </c>
       <c r="AU150" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV150" s="6">
         <v>0</v>
@@ -68547,7 +68547,7 @@
         <v>0</v>
       </c>
       <c r="AX150" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY150" s="6">
         <v>0</v>
@@ -68556,7 +68556,7 @@
         <v>0</v>
       </c>
       <c r="BA150" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB150" s="6">
         <v>0</v>
@@ -68565,7 +68565,7 @@
         <v>0</v>
       </c>
       <c r="BD150" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BE150" s="6">
         <v>0</v>
@@ -68574,7 +68574,7 @@
         <v>0</v>
       </c>
       <c r="BG150" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BH150" s="6">
         <v>0</v>
@@ -68583,7 +68583,7 @@
         <v>0</v>
       </c>
       <c r="BJ150" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BK150" s="6">
         <v>0</v>
@@ -68592,7 +68592,7 @@
         <v>0</v>
       </c>
       <c r="BM150" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BN150" s="6">
         <v>0</v>
@@ -68601,7 +68601,7 @@
         <v>0</v>
       </c>
       <c r="BP150" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BQ150" s="6">
         <v>0</v>
@@ -68610,7 +68610,7 @@
         <v>0</v>
       </c>
       <c r="BS150" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BT150" s="6">
         <v>0</v>
@@ -68619,16 +68619,16 @@
         <v>0</v>
       </c>
       <c r="BV150" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BW150" s="6">
         <v>0</v>
       </c>
       <c r="BX150" s="6">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="BY150" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BZ150" s="6">
         <v>0</v>
@@ -68637,7 +68637,7 @@
         <v>0</v>
       </c>
       <c r="CB150" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CC150" s="6">
         <v>0</v>
@@ -68646,7 +68646,7 @@
         <v>0</v>
       </c>
       <c r="CE150" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CF150" s="6">
         <v>0</v>
@@ -68655,7 +68655,7 @@
         <v>0</v>
       </c>
       <c r="CH150" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CI150" s="6">
         <v>0</v>
@@ -68664,7 +68664,7 @@
         <v>0</v>
       </c>
       <c r="CK150" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CL150" s="6">
         <v>0</v>
@@ -68673,7 +68673,7 @@
         <v>0</v>
       </c>
       <c r="CN150" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CO150" s="6">
         <v>0</v>
@@ -68682,7 +68682,7 @@
         <v>0</v>
       </c>
       <c r="CQ150" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CR150" s="6">
         <v>0</v>
@@ -68691,7 +68691,7 @@
         <v>0</v>
       </c>
       <c r="CT150" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CU150" s="6">
         <v>0</v>
@@ -68700,7 +68700,7 @@
         <v>0</v>
       </c>
       <c r="CW150" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CX150" s="6">
         <v>0</v>
@@ -68709,7 +68709,7 @@
         <v>0</v>
       </c>
       <c r="CZ150" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DA150" s="6">
         <v>0</v>
@@ -68718,7 +68718,7 @@
         <v>0</v>
       </c>
       <c r="DC150" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DD150" s="6">
         <v>0</v>
@@ -68727,7 +68727,7 @@
         <v>0</v>
       </c>
       <c r="DF150" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DG150" s="6">
         <v>0</v>
@@ -68736,7 +68736,7 @@
         <v>0</v>
       </c>
       <c r="DI150" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DJ150" s="6">
         <v>0</v>
@@ -68745,7 +68745,7 @@
         <v>0</v>
       </c>
       <c r="DL150" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DM150" s="6">
         <v>0</v>
@@ -68754,7 +68754,7 @@
         <v>0</v>
       </c>
       <c r="DO150" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DP150" s="6">
         <v>0</v>
@@ -68763,7 +68763,7 @@
         <v>0</v>
       </c>
       <c r="DR150" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS150" s="6">
         <v>0</v>
@@ -68772,7 +68772,7 @@
         <v>0</v>
       </c>
       <c r="DU150" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DV150" s="6">
         <v>0</v>
@@ -68781,7 +68781,7 @@
         <v>0</v>
       </c>
       <c r="DX150" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DY150" s="6">
         <v>0</v>
@@ -68790,7 +68790,7 @@
         <v>0</v>
       </c>
       <c r="EA150" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EB150" s="6">
         <v>0</v>
@@ -68799,7 +68799,7 @@
         <v>0</v>
       </c>
       <c r="ED150" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EE150" s="6">
         <v>0</v>
@@ -68808,7 +68808,7 @@
         <v>0</v>
       </c>
       <c r="EG150" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EH150" s="6">
         <v>0</v>
@@ -68817,7 +68817,7 @@
         <v>0</v>
       </c>
       <c r="EJ150" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EK150" s="6">
         <v>0</v>
@@ -68826,7 +68826,7 @@
         <v>0</v>
       </c>
       <c r="EM150" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EN150" s="6">
         <v>0</v>
